--- a/Burgraben Parameters.xlsx
+++ b/Burgraben Parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/au652733/Python/Project_julia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F542C0-8342-FE4B-BE7E-1FE77622F701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457D9870-091B-1C48-9051-0AE6876C88D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{E5675EDA-2BBE-479E-8689-D342BA924728}"/>
   </bookViews>
@@ -805,7 +805,7 @@
       <c r="C11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <f>D10*10^-6/(10^-2)</f>
         <v>0.14549999999999999</v>
       </c>
